--- a/projeto_hotel/projetohotel.lays2B/db/clienteS.xlSx
+++ b/projeto_hotel/projetohotel.lays2B/db/clienteS.xlSx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,86 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Data Cadastro</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>lays</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>18288737237373</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>lays@gmail</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>11727773737373</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>06ykihjhkjhkmhtmkhbmkbhmkmkb</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>d,d,l,lferfe,l</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lays</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1524244344334</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jhdhidhji@jdddjjd</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>524234242456</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ideikjhdjhkefej</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>nfehehhegrhf</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>

--- a/projeto_hotel/projetohotel.lays2B/db/clienteS.xlSx
+++ b/projeto_hotel/projetohotel.lays2B/db/clienteS.xlSx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,46 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lays</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>172737584848</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>lajjd@kdkd</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>19298474636</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>kdiieie</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>rrrertg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
